--- a/src/assets/Zonificacion/codigos zonas.xlsx
+++ b/src/assets/Zonificacion/codigos zonas.xlsx
@@ -8,18 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nicol\Desktop\Coding Project\PROYECTAMOS\Valle de Aburrá\visor-amva\src\assets\Zonificacion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BD31BA3-2FE8-4AEA-95EF-6496D67905EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCD5F1DA-0E82-463F-A29C-577F4D087513}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="municipio" sheetId="1" r:id="rId1"/>
     <sheet name="zonas sit" sheetId="2" r:id="rId2"/>
     <sheet name="macozonas" sheetId="3" r:id="rId3"/>
-    <sheet name="SIT ext Antioquia y resto pais " sheetId="4" r:id="rId4"/>
+    <sheet name="Hoja1" sheetId="5" r:id="rId4"/>
+    <sheet name="SIT ext Antioquia y resto pais " sheetId="4" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">macozonas!$A$1:$E$67</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Hoja1!$A$1:$C$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Hoja1!$A$1:$C$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'zonas sit'!$A$1:$C$537</definedName>
   </definedNames>
   <calcPr calcId="191029" concurrentCalc="0"/>
@@ -43,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1200" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1335" uniqueCount="233">
   <si>
     <t xml:space="preserve">Municipio </t>
   </si>
@@ -538,6 +540,210 @@
   </si>
   <si>
     <t>Id Macrozona 2017</t>
+  </si>
+  <si>
+    <t>Girardota - Rural</t>
+  </si>
+  <si>
+    <t>Girardota - Urbana</t>
+  </si>
+  <si>
+    <t>Id Real Macrozona 2017</t>
+  </si>
+  <si>
+    <t>Barbosa - Urbana</t>
+  </si>
+  <si>
+    <t>Barbosa - Rural</t>
+  </si>
+  <si>
+    <t>Copacabana - Rural</t>
+  </si>
+  <si>
+    <t>Copacabana - Urbana</t>
+  </si>
+  <si>
+    <t>Caldas - Urbana</t>
+  </si>
+  <si>
+    <t>Caldas - Rural</t>
+  </si>
+  <si>
+    <t>Medellín - El Poblado</t>
+  </si>
+  <si>
+    <t>Medellín - Guayabal</t>
+  </si>
+  <si>
+    <t>Medellín - Belén</t>
+  </si>
+  <si>
+    <t>Medellín - Corregimiento San Sebastián</t>
+  </si>
+  <si>
+    <t>Medellín - Corregimiento San Cristóbal</t>
+  </si>
+  <si>
+    <t>Medellín - Corregimiento Altavista</t>
+  </si>
+  <si>
+    <t>Medellín - Corregimiento San Antonio</t>
+  </si>
+  <si>
+    <t>Medellín - Corregimiento Santa Elena</t>
+  </si>
+  <si>
+    <t>Medellín - San Javier</t>
+  </si>
+  <si>
+    <t>Medellín - Laureles-Estadio</t>
+  </si>
+  <si>
+    <t>Medellín - La Candelaria</t>
+  </si>
+  <si>
+    <t>Medellín - Aranjuez</t>
+  </si>
+  <si>
+    <t>Medellín - Robledo</t>
+  </si>
+  <si>
+    <t>Medellín - Doce de Octubre</t>
+  </si>
+  <si>
+    <t>Medellín - Buenos Aires</t>
+  </si>
+  <si>
+    <t>Medellín - Villa Hermosa</t>
+  </si>
+  <si>
+    <t>Medellín - Manrique</t>
+  </si>
+  <si>
+    <t>Medellín - Popular</t>
+  </si>
+  <si>
+    <t>Medellín - Santa Cruz</t>
+  </si>
+  <si>
+    <t>Medellín - La América</t>
+  </si>
+  <si>
+    <t>Medellín - Castilla</t>
+  </si>
+  <si>
+    <t>Envigado - Vereda El Vallano</t>
+  </si>
+  <si>
+    <t>Envigado - Vereda El Escobero</t>
+  </si>
+  <si>
+    <t>Envigado - Vereda Perico y Pantanillo</t>
+  </si>
+  <si>
+    <t>Envigado - Vereda Las Palmas</t>
+  </si>
+  <si>
+    <t>Envigado - El Esmeraldal</t>
+  </si>
+  <si>
+    <t>Envigado - La Inmaculada</t>
+  </si>
+  <si>
+    <t>Envigado - Las Flores - Alto de Misael</t>
+  </si>
+  <si>
+    <t>Envigado - El Dorado - La Paz</t>
+  </si>
+  <si>
+    <t>Envigado - San José</t>
+  </si>
+  <si>
+    <t>Envigado - Z. Centro</t>
+  </si>
+  <si>
+    <t>Envigado - San Marcos</t>
+  </si>
+  <si>
+    <t>Envigado - Las Vegas</t>
+  </si>
+  <si>
+    <t>Envigado - Alcalá</t>
+  </si>
+  <si>
+    <t>Itagüí - Rural</t>
+  </si>
+  <si>
+    <t>Itagüí - Z. Centro</t>
+  </si>
+  <si>
+    <t>Itagüí - San Francisco</t>
+  </si>
+  <si>
+    <t>Itagüí - San Pio</t>
+  </si>
+  <si>
+    <t>Itagüí - Santa Maria</t>
+  </si>
+  <si>
+    <t>La Estrella - Urbana</t>
+  </si>
+  <si>
+    <t>Sabaneta - Urbana</t>
+  </si>
+  <si>
+    <t>Sabaneta - Rural</t>
+  </si>
+  <si>
+    <t>La Estrella - Rural</t>
+  </si>
+  <si>
+    <t>Bello - Paris</t>
+  </si>
+  <si>
+    <t>Bello - Madera</t>
+  </si>
+  <si>
+    <t>Bello - Santa Ana</t>
+  </si>
+  <si>
+    <t>Bello - La Cumbre - El Carmelo</t>
+  </si>
+  <si>
+    <t>Bello - Bellavista</t>
+  </si>
+  <si>
+    <t>Bello - Altos de Niquía</t>
+  </si>
+  <si>
+    <t>Bello - Niquía</t>
+  </si>
+  <si>
+    <t>Bello - Fontidueño</t>
+  </si>
+  <si>
+    <t>Bello - Acevedo</t>
+  </si>
+  <si>
+    <t>Bello - Rural</t>
+  </si>
+  <si>
+    <t>Bello - Croacia - El Pinar</t>
+  </si>
+  <si>
+    <t>Bello - Centro Bello</t>
+  </si>
+  <si>
+    <t>Bello - Guasimalito</t>
+  </si>
+  <si>
+    <t>Itagüí - Calatrava</t>
+  </si>
+  <si>
+    <t>Itagüí - El Rosario</t>
+  </si>
+  <si>
+    <t>*</t>
   </si>
 </sst>
 </file>
@@ -674,7 +880,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -710,15 +916,6 @@
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -735,11 +932,29 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1064,7 +1279,7 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="18">
+      <c r="A2" s="15">
         <v>1</v>
       </c>
       <c r="B2" s="9" t="s">
@@ -1072,7 +1287,7 @@
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="18">
+      <c r="A3" s="15">
         <v>79</v>
       </c>
       <c r="B3" s="9" t="s">
@@ -1080,7 +1295,7 @@
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="18">
+      <c r="A4" s="15">
         <v>88</v>
       </c>
       <c r="B4" s="9" t="s">
@@ -1088,7 +1303,7 @@
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="18">
+      <c r="A5" s="15">
         <v>129</v>
       </c>
       <c r="B5" s="9" t="s">
@@ -1096,7 +1311,7 @@
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="18">
+      <c r="A6" s="15">
         <v>212</v>
       </c>
       <c r="B6" s="9" t="s">
@@ -1104,7 +1319,7 @@
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="18">
+      <c r="A7" s="15">
         <v>266</v>
       </c>
       <c r="B7" s="9" t="s">
@@ -1112,7 +1327,7 @@
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="18">
+      <c r="A8" s="15">
         <v>308</v>
       </c>
       <c r="B8" s="9" t="s">
@@ -1120,7 +1335,7 @@
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="18">
+      <c r="A9" s="15">
         <v>360</v>
       </c>
       <c r="B9" s="9" t="s">
@@ -1128,7 +1343,7 @@
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="18">
+      <c r="A10" s="15">
         <v>380</v>
       </c>
       <c r="B10" s="9" t="s">
@@ -1136,7 +1351,7 @@
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" s="18">
+      <c r="A11" s="15">
         <v>631</v>
       </c>
       <c r="B11" s="9" t="s">
@@ -7027,17 +7242,18 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:I67"/>
+  <dimension ref="A1:J67"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.44140625" style="12" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="37.88671875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.77734375" style="23" customWidth="1"/>
-    <col min="9" max="9" width="47.21875" style="23" customWidth="1"/>
+    <col min="8" max="8" width="19.77734375" style="20" customWidth="1"/>
+    <col min="9" max="9" width="47.21875" style="20" customWidth="1"/>
+    <col min="10" max="10" width="45.109375" style="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="11" t="s">
         <v>125</v>
       </c>
@@ -7053,14 +7269,8 @@
       <c r="E1" t="s">
         <v>129</v>
       </c>
-      <c r="H1" s="20" t="s">
-        <v>125</v>
-      </c>
-      <c r="I1" s="20" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="8">
         <v>1</v>
       </c>
@@ -7077,16 +7287,8 @@
       <c r="E2" t="s">
         <v>141</v>
       </c>
-      <c r="H2" s="21">
-        <f>A2</f>
-        <v>1</v>
-      </c>
-      <c r="I2" s="22" t="str">
-        <f>_xlfn.CONCAT(D2," - ",E2)</f>
-        <v>Itagüí - El Rosario</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="8">
         <v>2</v>
       </c>
@@ -7103,16 +7305,8 @@
       <c r="E3" t="s">
         <v>144</v>
       </c>
-      <c r="H3" s="21">
-        <f t="shared" ref="H3:H66" si="0">A3</f>
-        <v>2</v>
-      </c>
-      <c r="I3" s="22" t="str">
-        <f t="shared" ref="I3:I66" si="1">_xlfn.CONCAT(D3," - ",E3)</f>
-        <v>Itagüí - Calatrava</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="8">
         <v>3</v>
       </c>
@@ -7129,16 +7323,8 @@
       <c r="E4" t="s">
         <v>143</v>
       </c>
-      <c r="H4" s="21">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="I4" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>Itagüí - Santa Maria</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="8">
         <v>4</v>
       </c>
@@ -7155,16 +7341,8 @@
       <c r="E5" t="s">
         <v>140</v>
       </c>
-      <c r="H5" s="21">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="I5" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>Itagüí - San Francisco</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="8">
         <v>5</v>
       </c>
@@ -7181,16 +7359,8 @@
       <c r="E6" t="s">
         <v>145</v>
       </c>
-      <c r="H6" s="21">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="I6" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>Bello - La Cumbre - El Carmelo</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="8">
         <v>6</v>
       </c>
@@ -7207,16 +7377,8 @@
       <c r="E7" t="s">
         <v>133</v>
       </c>
-      <c r="H7" s="21">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="I7" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>Bello - Bellavista</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="8">
         <v>7</v>
       </c>
@@ -7233,16 +7395,8 @@
       <c r="E8" t="s">
         <v>139</v>
       </c>
-      <c r="H8" s="21">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="I8" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>Itagüí - San Pio</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="8">
         <v>8</v>
       </c>
@@ -7259,16 +7413,8 @@
       <c r="E9" t="s">
         <v>132</v>
       </c>
-      <c r="H9" s="21">
-        <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="I9" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>Bello - Santa Ana</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="8">
         <v>9</v>
       </c>
@@ -7285,16 +7431,8 @@
       <c r="E10" t="s">
         <v>134</v>
       </c>
-      <c r="H10" s="21">
-        <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="I10" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>Bello - Altos de Niquía</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="8">
         <v>10</v>
       </c>
@@ -7311,16 +7449,8 @@
       <c r="E11" t="s">
         <v>147</v>
       </c>
-      <c r="H11" s="21">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="I11" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>Bello - Centro Bello</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="8">
         <v>11</v>
       </c>
@@ -7334,20 +7464,12 @@
         <f>VLOOKUP(C12,municipio!$A$2:$B$11,2)</f>
         <v>Medellín</v>
       </c>
-      <c r="E12" s="19" t="str">
-        <f>B12</f>
+      <c r="E12" s="16" t="str">
+        <f t="shared" ref="E12:E23" si="0">B12</f>
         <v>Robledo</v>
       </c>
-      <c r="H12" s="21">
-        <f t="shared" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="I12" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>Medellín - Robledo</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="8">
         <v>12</v>
       </c>
@@ -7361,20 +7483,12 @@
         <f>VLOOKUP(C13,municipio!$A$2:$B$11,2)</f>
         <v>Medellín</v>
       </c>
-      <c r="E13" s="19" t="str">
-        <f>B13</f>
+      <c r="E13" s="16" t="str">
+        <f t="shared" si="0"/>
         <v>El Poblado</v>
       </c>
-      <c r="H13" s="21">
-        <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="I13" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>Medellín - El Poblado</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="8">
         <v>13</v>
       </c>
@@ -7388,20 +7502,12 @@
         <f>VLOOKUP(C14,municipio!$A$2:$B$11,2)</f>
         <v>Medellín</v>
       </c>
-      <c r="E14" s="19" t="str">
-        <f>B14</f>
+      <c r="E14" s="16" t="str">
+        <f t="shared" si="0"/>
         <v>Manrique</v>
       </c>
-      <c r="H14" s="21">
-        <f t="shared" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="I14" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>Medellín - Manrique</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="8">
         <v>14</v>
       </c>
@@ -7415,20 +7521,12 @@
         <f>VLOOKUP(C15,municipio!$A$2:$B$11,2)</f>
         <v>Medellín</v>
       </c>
-      <c r="E15" s="19" t="str">
-        <f>B15</f>
+      <c r="E15" s="16" t="str">
+        <f t="shared" si="0"/>
         <v>Guayabal</v>
       </c>
-      <c r="H15" s="21">
-        <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="I15" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>Medellín - Guayabal</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="8">
         <v>15</v>
       </c>
@@ -7442,20 +7540,12 @@
         <f>VLOOKUP(C16,municipio!$A$2:$B$11,2)</f>
         <v>Medellín</v>
       </c>
-      <c r="E16" s="19" t="str">
-        <f>B16</f>
+      <c r="E16" s="16" t="str">
+        <f t="shared" si="0"/>
         <v>Buenos Aires</v>
       </c>
-      <c r="H16" s="21">
-        <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="I16" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>Medellín - Buenos Aires</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="8">
         <v>16</v>
       </c>
@@ -7469,20 +7559,12 @@
         <f>VLOOKUP(C17,municipio!$A$2:$B$11,2)</f>
         <v>Medellín</v>
       </c>
-      <c r="E17" s="19" t="str">
-        <f>B17</f>
+      <c r="E17" s="16" t="str">
+        <f t="shared" si="0"/>
         <v>Belén</v>
       </c>
-      <c r="H17" s="21">
-        <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="I17" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>Medellín - Belén</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="8">
         <v>17</v>
       </c>
@@ -7496,20 +7578,12 @@
         <f>VLOOKUP(C18,municipio!$A$2:$B$11,2)</f>
         <v>Medellín</v>
       </c>
-      <c r="E18" s="19" t="str">
-        <f>B18</f>
+      <c r="E18" s="16" t="str">
+        <f t="shared" si="0"/>
         <v>Aranjuez</v>
       </c>
-      <c r="H18" s="21">
-        <f t="shared" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="I18" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>Medellín - Aranjuez</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="8">
         <v>18</v>
       </c>
@@ -7523,20 +7597,12 @@
         <f>VLOOKUP(C19,municipio!$A$2:$B$11,2)</f>
         <v>Medellín</v>
       </c>
-      <c r="E19" s="19" t="str">
-        <f>B19</f>
+      <c r="E19" s="16" t="str">
+        <f t="shared" si="0"/>
         <v>La América</v>
       </c>
-      <c r="H19" s="21">
-        <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="I19" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>Medellín - La América</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="8">
         <v>19</v>
       </c>
@@ -7550,20 +7616,12 @@
         <f>VLOOKUP(C20,municipio!$A$2:$B$11,2)</f>
         <v>Medellín</v>
       </c>
-      <c r="E20" s="19" t="str">
-        <f>B20</f>
+      <c r="E20" s="16" t="str">
+        <f t="shared" si="0"/>
         <v>La Candelaria</v>
       </c>
-      <c r="H20" s="21">
-        <f t="shared" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="I20" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>Medellín - La Candelaria</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="8">
         <v>20</v>
       </c>
@@ -7577,20 +7635,12 @@
         <f>VLOOKUP(C21,municipio!$A$2:$B$11,2)</f>
         <v>Medellín</v>
       </c>
-      <c r="E21" s="19" t="str">
-        <f>B21</f>
+      <c r="E21" s="16" t="str">
+        <f t="shared" si="0"/>
         <v>Villa Hermosa</v>
       </c>
-      <c r="H21" s="21">
-        <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="I21" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>Medellín - Villa Hermosa</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="8">
         <v>21</v>
       </c>
@@ -7604,20 +7654,12 @@
         <f>VLOOKUP(C22,municipio!$A$2:$B$11,2)</f>
         <v>Medellín</v>
       </c>
-      <c r="E22" s="19" t="str">
-        <f>B22</f>
+      <c r="E22" s="16" t="str">
+        <f t="shared" si="0"/>
         <v>Laureles-Estadio</v>
       </c>
-      <c r="H22" s="21">
-        <f t="shared" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="I22" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>Medellín - Laureles-Estadio</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="8">
         <v>22</v>
       </c>
@@ -7631,20 +7673,12 @@
         <f>VLOOKUP(C23,municipio!$A$2:$B$11,2)</f>
         <v>Medellín</v>
       </c>
-      <c r="E23" s="19" t="str">
-        <f>B23</f>
+      <c r="E23" s="16" t="str">
+        <f t="shared" si="0"/>
         <v>San Javier</v>
       </c>
-      <c r="H23" s="21">
-        <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="I23" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>Medellín - San Javier</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="8">
         <v>23</v>
       </c>
@@ -7661,16 +7695,8 @@
       <c r="E24" t="s">
         <v>142</v>
       </c>
-      <c r="H24" s="21">
-        <f t="shared" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="I24" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>Itagüí - Z. Centro</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="8">
         <v>24</v>
       </c>
@@ -7684,20 +7710,12 @@
         <f>VLOOKUP(C25,municipio!$A$2:$B$11,2)</f>
         <v>Caldas</v>
       </c>
-      <c r="E25" s="19" t="str">
+      <c r="E25" s="16" t="str">
         <f>B25</f>
         <v>Urbana</v>
       </c>
-      <c r="H25" s="21">
-        <f t="shared" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="I25" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>Caldas - Urbana</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="8">
         <v>25</v>
       </c>
@@ -7711,20 +7729,12 @@
         <f>VLOOKUP(C26,municipio!$A$2:$B$11,2)</f>
         <v>La Estrella</v>
       </c>
-      <c r="E26" s="19" t="str">
+      <c r="E26" s="16" t="str">
         <f>B26</f>
         <v>Urbana</v>
       </c>
-      <c r="H26" s="21">
-        <f t="shared" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="I26" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>La Estrella - Urbana</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="8">
         <v>26</v>
       </c>
@@ -7738,20 +7748,12 @@
         <f>VLOOKUP(C27,municipio!$A$2:$B$11,2)</f>
         <v>Barbosa</v>
       </c>
-      <c r="E27" s="19" t="str">
+      <c r="E27" s="16" t="str">
         <f>B27</f>
         <v>Urbana</v>
       </c>
-      <c r="H27" s="21">
-        <f t="shared" si="0"/>
-        <v>26</v>
-      </c>
-      <c r="I27" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>Barbosa - Urbana</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="8">
         <v>27</v>
       </c>
@@ -7765,20 +7767,12 @@
         <f>VLOOKUP(C28,municipio!$A$2:$B$11,2)</f>
         <v>Girardota</v>
       </c>
-      <c r="E28" s="19" t="str">
+      <c r="E28" s="16" t="str">
         <f>B28</f>
         <v>Urbana</v>
       </c>
-      <c r="H28" s="21">
-        <f t="shared" si="0"/>
-        <v>27</v>
-      </c>
-      <c r="I28" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>Girardota - Urbana</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="8">
         <v>28</v>
       </c>
@@ -7795,16 +7789,8 @@
       <c r="E29" t="s">
         <v>137</v>
       </c>
-      <c r="H29" s="21">
-        <f t="shared" si="0"/>
-        <v>28</v>
-      </c>
-      <c r="I29" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>Bello - Madera</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="8">
         <v>29</v>
       </c>
@@ -7821,16 +7807,8 @@
       <c r="E30" t="s">
         <v>136</v>
       </c>
-      <c r="H30" s="21">
-        <f t="shared" si="0"/>
-        <v>29</v>
-      </c>
-      <c r="I30" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>Bello - Fontidueño</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="8">
         <v>30</v>
       </c>
@@ -7844,20 +7822,12 @@
         <f>VLOOKUP(C31,municipio!$A$2:$B$11,2)</f>
         <v>Medellín</v>
       </c>
-      <c r="E31" s="19" t="str">
+      <c r="E31" s="16" t="str">
         <f>B31</f>
         <v>Castilla</v>
       </c>
-      <c r="H31" s="21">
-        <f t="shared" si="0"/>
-        <v>30</v>
-      </c>
-      <c r="I31" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>Medellín - Castilla</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="8">
         <v>31</v>
       </c>
@@ -7871,20 +7841,12 @@
         <f>VLOOKUP(C32,municipio!$A$2:$B$11,2)</f>
         <v>Medellín</v>
       </c>
-      <c r="E32" s="19" t="str">
+      <c r="E32" s="16" t="str">
         <f>B32</f>
         <v>Popular</v>
       </c>
-      <c r="H32" s="21">
-        <f t="shared" si="0"/>
-        <v>31</v>
-      </c>
-      <c r="I32" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>Medellín - Popular</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="8">
         <v>32</v>
       </c>
@@ -7898,20 +7860,12 @@
         <f>VLOOKUP(C33,municipio!$A$2:$B$11,2)</f>
         <v>Medellín</v>
       </c>
-      <c r="E33" s="19" t="str">
+      <c r="E33" s="16" t="str">
         <f>B33</f>
         <v>Doce de Octubre</v>
       </c>
-      <c r="H33" s="21">
-        <f t="shared" si="0"/>
-        <v>32</v>
-      </c>
-      <c r="I33" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>Medellín - Doce de Octubre</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="8">
         <v>33</v>
       </c>
@@ -7925,20 +7879,12 @@
         <f>VLOOKUP(C34,municipio!$A$2:$B$11,2)</f>
         <v>Medellín</v>
       </c>
-      <c r="E34" s="19" t="str">
+      <c r="E34" s="16" t="str">
         <f>B34</f>
         <v>Santa Cruz</v>
       </c>
-      <c r="H34" s="21">
-        <f t="shared" si="0"/>
-        <v>33</v>
-      </c>
-      <c r="I34" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>Medellín - Santa Cruz</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="8">
         <v>34</v>
       </c>
@@ -7955,16 +7901,8 @@
       <c r="E35" t="s">
         <v>146</v>
       </c>
-      <c r="H35" s="21">
-        <f t="shared" si="0"/>
-        <v>34</v>
-      </c>
-      <c r="I35" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>Bello - Acevedo</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" s="8">
         <v>35</v>
       </c>
@@ -7978,20 +7916,12 @@
         <f>VLOOKUP(C36,municipio!$A$2:$B$11,2)</f>
         <v>Copacabana</v>
       </c>
-      <c r="E36" s="19" t="str">
+      <c r="E36" s="16" t="str">
         <f>B36</f>
         <v>Urbana</v>
       </c>
-      <c r="H36" s="21">
-        <f t="shared" si="0"/>
-        <v>35</v>
-      </c>
-      <c r="I36" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>Copacabana - Urbana</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" s="8">
         <v>36</v>
       </c>
@@ -8008,16 +7938,8 @@
       <c r="E37" t="s">
         <v>135</v>
       </c>
-      <c r="H37" s="21">
-        <f t="shared" si="0"/>
-        <v>36</v>
-      </c>
-      <c r="I37" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>Bello - Niquía</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" s="8">
         <v>37</v>
       </c>
@@ -8034,16 +7956,8 @@
       <c r="E38" t="s">
         <v>149</v>
       </c>
-      <c r="H38" s="21">
-        <f t="shared" si="0"/>
-        <v>37</v>
-      </c>
-      <c r="I38" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>Bello - Guasimalito</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" s="8">
         <v>38</v>
       </c>
@@ -8060,16 +7974,8 @@
       <c r="E39" t="s">
         <v>138</v>
       </c>
-      <c r="H39" s="21">
-        <f t="shared" si="0"/>
-        <v>38</v>
-      </c>
-      <c r="I39" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>Bello - Paris</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" s="8">
         <v>39</v>
       </c>
@@ -8086,16 +7992,8 @@
       <c r="E40" t="s">
         <v>148</v>
       </c>
-      <c r="H40" s="21">
-        <f t="shared" si="0"/>
-        <v>39</v>
-      </c>
-      <c r="I40" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>Bello - Croacia - El Pinar</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" s="8">
         <v>40</v>
       </c>
@@ -8109,20 +8007,12 @@
         <f>VLOOKUP(C41,municipio!$A$2:$B$11,2)</f>
         <v>Bello</v>
       </c>
-      <c r="E41" s="19" t="str">
-        <f>B41</f>
+      <c r="E41" s="16" t="str">
+        <f t="shared" ref="E41:E51" si="1">B41</f>
         <v>Rural</v>
       </c>
-      <c r="H41" s="21">
-        <f t="shared" si="0"/>
-        <v>40</v>
-      </c>
-      <c r="I41" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>Bello - Rural</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" s="8">
         <v>41</v>
       </c>
@@ -8136,20 +8026,12 @@
         <f>VLOOKUP(C42,municipio!$A$2:$B$11,2)</f>
         <v>Barbosa</v>
       </c>
-      <c r="E42" s="19" t="str">
-        <f>B42</f>
+      <c r="E42" s="16" t="str">
+        <f t="shared" si="1"/>
         <v>Rural</v>
       </c>
-      <c r="H42" s="21">
-        <f t="shared" si="0"/>
-        <v>41</v>
-      </c>
-      <c r="I42" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>Barbosa - Rural</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" s="8">
         <v>42</v>
       </c>
@@ -8163,20 +8045,12 @@
         <f>VLOOKUP(C43,municipio!$A$2:$B$11,2)</f>
         <v>Copacabana</v>
       </c>
-      <c r="E43" s="19" t="str">
-        <f>B43</f>
+      <c r="E43" s="16" t="str">
+        <f t="shared" si="1"/>
         <v>Rural</v>
       </c>
-      <c r="H43" s="21">
-        <f t="shared" si="0"/>
-        <v>42</v>
-      </c>
-      <c r="I43" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>Copacabana - Rural</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" s="8">
         <v>43</v>
       </c>
@@ -8190,20 +8064,12 @@
         <f>VLOOKUP(C44,municipio!$A$2:$B$11,2)</f>
         <v>Girardota</v>
       </c>
-      <c r="E44" s="19" t="str">
-        <f>B44</f>
+      <c r="E44" s="16" t="str">
+        <f t="shared" si="1"/>
         <v>Rural</v>
       </c>
-      <c r="H44" s="21">
-        <f t="shared" si="0"/>
-        <v>43</v>
-      </c>
-      <c r="I44" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>Girardota - Rural</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" s="8">
         <v>44</v>
       </c>
@@ -8217,20 +8083,12 @@
         <f>VLOOKUP(C45,municipio!$A$2:$B$11,2)</f>
         <v>Medellín</v>
       </c>
-      <c r="E45" s="19" t="str">
-        <f>B45</f>
+      <c r="E45" s="16" t="str">
+        <f t="shared" si="1"/>
         <v>Corregimiento San Sebastián</v>
       </c>
-      <c r="H45" s="21">
-        <f t="shared" si="0"/>
-        <v>44</v>
-      </c>
-      <c r="I45" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>Medellín - Corregimiento San Sebastián</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" s="8">
         <v>45</v>
       </c>
@@ -8244,20 +8102,12 @@
         <f>VLOOKUP(C46,municipio!$A$2:$B$11,2)</f>
         <v>Medellín</v>
       </c>
-      <c r="E46" s="19" t="str">
-        <f>B46</f>
+      <c r="E46" s="16" t="str">
+        <f t="shared" si="1"/>
         <v>Corregimiento San Cristóbal</v>
       </c>
-      <c r="H46" s="21">
-        <f t="shared" si="0"/>
-        <v>45</v>
-      </c>
-      <c r="I46" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>Medellín - Corregimiento San Cristóbal</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" s="8">
         <v>46</v>
       </c>
@@ -8271,20 +8121,12 @@
         <f>VLOOKUP(C47,municipio!$A$2:$B$11,2)</f>
         <v>Medellín</v>
       </c>
-      <c r="E47" s="19" t="str">
-        <f>B47</f>
+      <c r="E47" s="16" t="str">
+        <f t="shared" si="1"/>
         <v>Corregimiento Altavista</v>
       </c>
-      <c r="H47" s="21">
-        <f t="shared" si="0"/>
-        <v>46</v>
-      </c>
-      <c r="I47" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>Medellín - Corregimiento Altavista</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" s="8">
         <v>47</v>
       </c>
@@ -8298,20 +8140,12 @@
         <f>VLOOKUP(C48,municipio!$A$2:$B$11,2)</f>
         <v>Medellín</v>
       </c>
-      <c r="E48" s="19" t="str">
-        <f>B48</f>
+      <c r="E48" s="16" t="str">
+        <f t="shared" si="1"/>
         <v>Corregimiento Santa Elena</v>
       </c>
-      <c r="H48" s="21">
-        <f t="shared" si="0"/>
-        <v>47</v>
-      </c>
-      <c r="I48" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>Medellín - Corregimiento Santa Elena</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" s="8">
         <v>48</v>
       </c>
@@ -8325,20 +8159,12 @@
         <f>VLOOKUP(C49,municipio!$A$2:$B$11,2)</f>
         <v>Medellín</v>
       </c>
-      <c r="E49" s="19" t="str">
-        <f>B49</f>
+      <c r="E49" s="16" t="str">
+        <f t="shared" si="1"/>
         <v>Corregimiento San Antonio</v>
       </c>
-      <c r="H49" s="21">
-        <f t="shared" si="0"/>
-        <v>48</v>
-      </c>
-      <c r="I49" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>Medellín - Corregimiento San Antonio</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" s="8">
         <v>49</v>
       </c>
@@ -8352,20 +8178,12 @@
         <f>VLOOKUP(C50,municipio!$A$2:$B$11,2)</f>
         <v>Itagüí</v>
       </c>
-      <c r="E50" s="19" t="str">
-        <f>B50</f>
+      <c r="E50" s="16" t="str">
+        <f t="shared" si="1"/>
         <v>Rural</v>
       </c>
-      <c r="H50" s="21">
-        <f t="shared" si="0"/>
-        <v>49</v>
-      </c>
-      <c r="I50" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>Itagüí - Rural</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" s="8">
         <v>50</v>
       </c>
@@ -8379,20 +8197,12 @@
         <f>VLOOKUP(C51,municipio!$A$2:$B$11,2)</f>
         <v>La Estrella</v>
       </c>
-      <c r="E51" s="19" t="str">
-        <f>B51</f>
+      <c r="E51" s="16" t="str">
+        <f t="shared" si="1"/>
         <v>Rural</v>
       </c>
-      <c r="H51" s="21">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-      <c r="I51" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>La Estrella - Rural</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" s="8">
         <v>51</v>
       </c>
@@ -8409,16 +8219,8 @@
       <c r="E52" t="s">
         <v>160</v>
       </c>
-      <c r="H52" s="21">
-        <f t="shared" si="0"/>
-        <v>51</v>
-      </c>
-      <c r="I52" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>Envigado - Las Vegas</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" s="8">
         <v>52</v>
       </c>
@@ -8435,16 +8237,8 @@
       <c r="E53" t="s">
         <v>161</v>
       </c>
-      <c r="H53" s="21">
-        <f t="shared" si="0"/>
-        <v>52</v>
-      </c>
-      <c r="I53" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>Envigado - San José</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" s="8">
         <v>53</v>
       </c>
@@ -8461,16 +8255,8 @@
       <c r="E54" t="s">
         <v>150</v>
       </c>
-      <c r="H54" s="21">
-        <f t="shared" si="0"/>
-        <v>53</v>
-      </c>
-      <c r="I54" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>Envigado - El Dorado - La Paz</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55" s="8">
         <v>54</v>
       </c>
@@ -8487,16 +8273,8 @@
       <c r="E55" t="s">
         <v>156</v>
       </c>
-      <c r="H55" s="21">
-        <f t="shared" si="0"/>
-        <v>54</v>
-      </c>
-      <c r="I55" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>Envigado - Alcalá</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" s="8">
         <v>55</v>
       </c>
@@ -8513,16 +8291,8 @@
       <c r="E56" t="s">
         <v>159</v>
       </c>
-      <c r="H56" s="21">
-        <f t="shared" si="0"/>
-        <v>55</v>
-      </c>
-      <c r="I56" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>Envigado - Las Flores - Alto de Misael</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57" s="8">
         <v>56</v>
       </c>
@@ -8539,16 +8309,8 @@
       <c r="E57" t="s">
         <v>157</v>
       </c>
-      <c r="H57" s="21">
-        <f t="shared" si="0"/>
-        <v>56</v>
-      </c>
-      <c r="I57" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>Envigado - El Esmeraldal</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58" s="8">
         <v>57</v>
       </c>
@@ -8565,16 +8327,8 @@
       <c r="E58" t="s">
         <v>142</v>
       </c>
-      <c r="H58" s="21">
-        <f t="shared" si="0"/>
-        <v>57</v>
-      </c>
-      <c r="I58" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>Envigado - Z. Centro</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59" s="8">
         <v>58</v>
       </c>
@@ -8591,16 +8345,8 @@
       <c r="E59" t="s">
         <v>151</v>
       </c>
-      <c r="H59" s="21">
-        <f t="shared" si="0"/>
-        <v>58</v>
-      </c>
-      <c r="I59" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>Envigado - San Marcos</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" s="8">
         <v>59</v>
       </c>
@@ -8617,16 +8363,8 @@
       <c r="E60" t="s">
         <v>158</v>
       </c>
-      <c r="H60" s="21">
-        <f t="shared" si="0"/>
-        <v>59</v>
-      </c>
-      <c r="I60" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>Envigado - La Inmaculada</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" s="8">
         <v>60</v>
       </c>
@@ -8643,16 +8381,8 @@
       <c r="E61" t="s">
         <v>154</v>
       </c>
-      <c r="H61" s="21">
-        <f t="shared" si="0"/>
-        <v>60</v>
-      </c>
-      <c r="I61" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>Envigado - Vereda Las Palmas</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" s="8">
         <v>61</v>
       </c>
@@ -8669,16 +8399,8 @@
       <c r="E62" t="s">
         <v>152</v>
       </c>
-      <c r="H62" s="21">
-        <f t="shared" si="0"/>
-        <v>61</v>
-      </c>
-      <c r="I62" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>Envigado - Vereda El Escobero</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63" s="8">
         <v>62</v>
       </c>
@@ -8695,16 +8417,8 @@
       <c r="E63" t="s">
         <v>153</v>
       </c>
-      <c r="H63" s="21">
-        <f t="shared" si="0"/>
-        <v>62</v>
-      </c>
-      <c r="I63" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>Envigado - Vereda El Vallano</v>
-      </c>
-    </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64" s="8">
         <v>63</v>
       </c>
@@ -8721,16 +8435,8 @@
       <c r="E64" t="s">
         <v>155</v>
       </c>
-      <c r="H64" s="21">
-        <f t="shared" si="0"/>
-        <v>63</v>
-      </c>
-      <c r="I64" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>Envigado - Vereda Perico y Pantanillo</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" s="8">
         <v>64</v>
       </c>
@@ -8744,20 +8450,12 @@
         <f>VLOOKUP(C65,municipio!$A$2:$B$11,2)</f>
         <v>Sabaneta</v>
       </c>
-      <c r="E65" s="19" t="str">
+      <c r="E65" s="16" t="str">
         <f>B65</f>
         <v>Urbana</v>
       </c>
-      <c r="H65" s="21">
-        <f t="shared" si="0"/>
-        <v>64</v>
-      </c>
-      <c r="I65" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>Sabaneta - Urbana</v>
-      </c>
-    </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66" s="8">
         <v>65</v>
       </c>
@@ -8771,20 +8469,12 @@
         <f>VLOOKUP(C66,municipio!$A$2:$B$11,2)</f>
         <v>Sabaneta</v>
       </c>
-      <c r="E66" s="19" t="str">
+      <c r="E66" s="16" t="str">
         <f>B66</f>
         <v>Rural</v>
       </c>
-      <c r="H66" s="21">
-        <f t="shared" si="0"/>
-        <v>65</v>
-      </c>
-      <c r="I66" s="22" t="str">
-        <f t="shared" si="1"/>
-        <v>Sabaneta - Rural</v>
-      </c>
-    </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67" s="8">
         <v>66</v>
       </c>
@@ -8798,30 +8488,1120 @@
         <f>VLOOKUP(C67,municipio!$A$2:$B$11,2)</f>
         <v>Caldas</v>
       </c>
-      <c r="E67" s="19" t="str">
+      <c r="E67" s="16" t="str">
         <f>B67</f>
         <v>Rural</v>
       </c>
-      <c r="H67" s="21">
-        <f t="shared" ref="H67" si="2">A67</f>
-        <v>66</v>
-      </c>
-      <c r="I67" s="22" t="str">
-        <f t="shared" ref="I67" si="3">_xlfn.CONCAT(D67," - ",E67)</f>
-        <v>Caldas - Rural</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E67" xr:uid="{00000000-0001-0000-0200-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E67">
-      <sortCondition ref="A1:A67"/>
-    </sortState>
-  </autoFilter>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="H2:J67">
+    <sortCondition ref="I1:I67"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{443896CA-5C07-4245-B3AF-BB7D297B88CA}">
+  <dimension ref="A1:G67"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="24.109375" customWidth="1"/>
+    <col min="2" max="2" width="42.88671875" customWidth="1"/>
+    <col min="3" max="3" width="36.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="17" t="s">
+        <v>125</v>
+      </c>
+      <c r="B1" s="17" t="s">
+        <v>164</v>
+      </c>
+      <c r="C1" s="17" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="18">
+        <f>macozonas!A42</f>
+        <v>41</v>
+      </c>
+      <c r="B2" s="19" t="str">
+        <f>_xlfn.CONCAT(macozonas!D42," - ",macozonas!E42)</f>
+        <v>Barbosa - Rural</v>
+      </c>
+      <c r="C2" s="19" t="s">
+        <v>170</v>
+      </c>
+      <c r="G2" s="19" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="18">
+        <f>macozonas!A27</f>
+        <v>26</v>
+      </c>
+      <c r="B3" s="19" t="str">
+        <f>_xlfn.CONCAT(macozonas!D27," - ",macozonas!E27)</f>
+        <v>Barbosa - Urbana</v>
+      </c>
+      <c r="C3" s="19" t="s">
+        <v>177</v>
+      </c>
+      <c r="G3" s="19" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="18">
+        <f>macozonas!A35</f>
+        <v>34</v>
+      </c>
+      <c r="B4" s="19" t="str">
+        <f>_xlfn.CONCAT(macozonas!D35," - ",macozonas!E35)</f>
+        <v>Bello - Acevedo</v>
+      </c>
+      <c r="C4" s="19" t="s">
+        <v>178</v>
+      </c>
+      <c r="G4" s="19" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="18">
+        <f>macozonas!A10</f>
+        <v>9</v>
+      </c>
+      <c r="B5" s="19" t="str">
+        <f>_xlfn.CONCAT(macozonas!D10," - ",macozonas!E10)</f>
+        <v>Bello - Altos de Niquía</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>179</v>
+      </c>
+      <c r="G5" s="19" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="18">
+        <f>macozonas!A7</f>
+        <v>6</v>
+      </c>
+      <c r="B6" s="19" t="str">
+        <f>_xlfn.CONCAT(macozonas!D7," - ",macozonas!E7)</f>
+        <v>Bello - Bellavista</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>180</v>
+      </c>
+      <c r="G6" s="19" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="18">
+        <f>macozonas!A11</f>
+        <v>10</v>
+      </c>
+      <c r="B7" s="19" t="str">
+        <f>_xlfn.CONCAT(macozonas!D11," - ",macozonas!E11)</f>
+        <v>Bello - Centro Bello</v>
+      </c>
+      <c r="C7" s="19" t="s">
+        <v>208</v>
+      </c>
+      <c r="G7" s="19" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="18">
+        <f>macozonas!A40</f>
+        <v>39</v>
+      </c>
+      <c r="B8" s="19" t="str">
+        <f>_xlfn.CONCAT(macozonas!D40," - ",macozonas!E40)</f>
+        <v>Bello - Croacia - El Pinar</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>206</v>
+      </c>
+      <c r="G8" s="19" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="18">
+        <f>macozonas!A30</f>
+        <v>29</v>
+      </c>
+      <c r="B9" s="19" t="str">
+        <f>_xlfn.CONCAT(macozonas!D30," - ",macozonas!E30)</f>
+        <v>Bello - Fontidueño</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>207</v>
+      </c>
+      <c r="G9" s="19" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="18">
+        <f>macozonas!A38</f>
+        <v>37</v>
+      </c>
+      <c r="B10" s="19" t="str">
+        <f>_xlfn.CONCAT(macozonas!D38," - ",macozonas!E38)</f>
+        <v>Bello - Guasimalito</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>202</v>
+      </c>
+      <c r="G10" s="19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="18">
+        <f>macozonas!A6</f>
+        <v>5</v>
+      </c>
+      <c r="B11" s="19" t="str">
+        <f>_xlfn.CONCAT(macozonas!D6," - ",macozonas!E6)</f>
+        <v>Bello - La Cumbre - El Carmelo</v>
+      </c>
+      <c r="C11" s="19" t="s">
+        <v>203</v>
+      </c>
+      <c r="G11" s="19" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="18">
+        <f>macozonas!A29</f>
+        <v>28</v>
+      </c>
+      <c r="B12" s="19" t="str">
+        <f>_xlfn.CONCAT(macozonas!D29," - ",macozonas!E29)</f>
+        <v>Bello - Madera</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>200</v>
+      </c>
+      <c r="G12" s="19" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="18">
+        <f>macozonas!A37</f>
+        <v>36</v>
+      </c>
+      <c r="B13" s="19" t="str">
+        <f>_xlfn.CONCAT(macozonas!D37," - ",macozonas!E37)</f>
+        <v>Bello - Niquía</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>201</v>
+      </c>
+      <c r="G13" s="19" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" s="18">
+        <f>macozonas!A39</f>
+        <v>38</v>
+      </c>
+      <c r="B14" s="19" t="str">
+        <f>_xlfn.CONCAT(macozonas!D39," - ",macozonas!E39)</f>
+        <v>Bello - Paris</v>
+      </c>
+      <c r="C14" s="19" t="s">
+        <v>204</v>
+      </c>
+      <c r="G14" s="19" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" s="18">
+        <f>macozonas!A41</f>
+        <v>40</v>
+      </c>
+      <c r="B15" s="19" t="str">
+        <f>_xlfn.CONCAT(macozonas!D41," - ",macozonas!E41)</f>
+        <v>Bello - Rural</v>
+      </c>
+      <c r="C15" s="19" t="s">
+        <v>205</v>
+      </c>
+      <c r="G15" s="19" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" s="18">
+        <f>macozonas!A9</f>
+        <v>8</v>
+      </c>
+      <c r="B16" s="19" t="str">
+        <f>_xlfn.CONCAT(macozonas!D9," - ",macozonas!E9)</f>
+        <v>Bello - Santa Ana</v>
+      </c>
+      <c r="C16" s="19" t="s">
+        <v>199</v>
+      </c>
+      <c r="G16" s="19" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" s="18">
+        <f>macozonas!A67</f>
+        <v>66</v>
+      </c>
+      <c r="B17" s="19" t="str">
+        <f>_xlfn.CONCAT(macozonas!D67," - ",macozonas!E67)</f>
+        <v>Caldas - Rural</v>
+      </c>
+      <c r="C17" s="19" t="s">
+        <v>196</v>
+      </c>
+      <c r="G17" s="19" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" s="18">
+        <f>macozonas!A25</f>
+        <v>24</v>
+      </c>
+      <c r="B18" s="19" t="str">
+        <f>_xlfn.CONCAT(macozonas!D25," - ",macozonas!E25)</f>
+        <v>Caldas - Urbana</v>
+      </c>
+      <c r="C18" s="19" t="s">
+        <v>197</v>
+      </c>
+      <c r="G18" s="19" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19" s="18">
+        <f>macozonas!A43</f>
+        <v>42</v>
+      </c>
+      <c r="B19" s="19" t="str">
+        <f>_xlfn.CONCAT(macozonas!D43," - ",macozonas!E43)</f>
+        <v>Copacabana - Rural</v>
+      </c>
+      <c r="C19" s="19" t="s">
+        <v>198</v>
+      </c>
+      <c r="G19" s="19" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" s="18">
+        <f>macozonas!A36</f>
+        <v>35</v>
+      </c>
+      <c r="B20" s="19" t="str">
+        <f>_xlfn.CONCAT(macozonas!D36," - ",macozonas!E36)</f>
+        <v>Copacabana - Urbana</v>
+      </c>
+      <c r="C20" s="19" t="s">
+        <v>195</v>
+      </c>
+      <c r="G20" s="19" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" s="18">
+        <f>macozonas!A55</f>
+        <v>54</v>
+      </c>
+      <c r="B21" s="19" t="str">
+        <f>_xlfn.CONCAT(macozonas!D55," - ",macozonas!E55)</f>
+        <v>Envigado - Alcalá</v>
+      </c>
+      <c r="C21" s="19" t="s">
+        <v>214</v>
+      </c>
+      <c r="G21" s="19" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22" s="18">
+        <f>macozonas!A54</f>
+        <v>53</v>
+      </c>
+      <c r="B22" s="19" t="str">
+        <f>_xlfn.CONCAT(macozonas!D54," - ",macozonas!E54)</f>
+        <v>Envigado - El Dorado - La Paz</v>
+      </c>
+      <c r="C22" s="19" t="s">
+        <v>215</v>
+      </c>
+      <c r="G22" s="19" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" s="18">
+        <f>macozonas!A57</f>
+        <v>56</v>
+      </c>
+      <c r="B23" s="19" t="str">
+        <f>_xlfn.CONCAT(macozonas!D57," - ",macozonas!E57)</f>
+        <v>Envigado - El Esmeraldal</v>
+      </c>
+      <c r="C23" s="19" t="s">
+        <v>183</v>
+      </c>
+      <c r="G23" s="19" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24" s="18">
+        <f>macozonas!A60</f>
+        <v>59</v>
+      </c>
+      <c r="B24" s="19" t="str">
+        <f>_xlfn.CONCAT(macozonas!D60," - ",macozonas!E60)</f>
+        <v>Envigado - La Inmaculada</v>
+      </c>
+      <c r="C24" s="19" t="s">
+        <v>209</v>
+      </c>
+      <c r="G24" s="19" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25" s="18">
+        <f>macozonas!A56</f>
+        <v>55</v>
+      </c>
+      <c r="B25" s="19" t="str">
+        <f>_xlfn.CONCAT(macozonas!D56," - ",macozonas!E56)</f>
+        <v>Envigado - Las Flores - Alto de Misael</v>
+      </c>
+      <c r="C25" s="19" t="s">
+        <v>211</v>
+      </c>
+      <c r="G25" s="19" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26" s="18">
+        <f>macozonas!A52</f>
+        <v>51</v>
+      </c>
+      <c r="B26" s="19" t="str">
+        <f>_xlfn.CONCAT(macozonas!D52," - ",macozonas!E52)</f>
+        <v>Envigado - Las Vegas</v>
+      </c>
+      <c r="C26" s="19" t="s">
+        <v>175</v>
+      </c>
+      <c r="G26" s="19" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A27" s="18">
+        <f>macozonas!A53</f>
+        <v>52</v>
+      </c>
+      <c r="B27" s="19" t="str">
+        <f>_xlfn.CONCAT(macozonas!D53," - ",macozonas!E53)</f>
+        <v>Envigado - San José</v>
+      </c>
+      <c r="C27" s="19" t="s">
+        <v>174</v>
+      </c>
+      <c r="G27" s="19" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A28" s="18">
+        <f>macozonas!A59</f>
+        <v>58</v>
+      </c>
+      <c r="B28" s="19" t="str">
+        <f>_xlfn.CONCAT(macozonas!D59," - ",macozonas!E59)</f>
+        <v>Envigado - San Marcos</v>
+      </c>
+      <c r="C28" s="19" t="s">
+        <v>176</v>
+      </c>
+      <c r="G28" s="19" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A29" s="18">
+        <f>macozonas!A62</f>
+        <v>61</v>
+      </c>
+      <c r="B29" s="19" t="str">
+        <f>_xlfn.CONCAT(macozonas!D62," - ",macozonas!E62)</f>
+        <v>Envigado - Vereda El Escobero</v>
+      </c>
+      <c r="C29" s="19" t="s">
+        <v>193</v>
+      </c>
+      <c r="G29" s="19" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A30" s="18">
+        <f>macozonas!A63</f>
+        <v>62</v>
+      </c>
+      <c r="B30" s="19" t="str">
+        <f>_xlfn.CONCAT(macozonas!D63," - ",macozonas!E63)</f>
+        <v>Envigado - Vereda El Vallano</v>
+      </c>
+      <c r="C30" s="19" t="s">
+        <v>182</v>
+      </c>
+      <c r="G30" s="19" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A31" s="18">
+        <f>macozonas!A61</f>
+        <v>60</v>
+      </c>
+      <c r="B31" s="19" t="str">
+        <f>_xlfn.CONCAT(macozonas!D61," - ",macozonas!E61)</f>
+        <v>Envigado - Vereda Las Palmas</v>
+      </c>
+      <c r="C31" s="19" t="s">
+        <v>185</v>
+      </c>
+      <c r="G31" s="19" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A32" s="18">
+        <f>macozonas!A64</f>
+        <v>63</v>
+      </c>
+      <c r="B32" s="19" t="str">
+        <f>_xlfn.CONCAT(macozonas!D64," - ",macozonas!E64)</f>
+        <v>Envigado - Vereda Perico y Pantanillo</v>
+      </c>
+      <c r="C32" s="19" t="s">
+        <v>194</v>
+      </c>
+      <c r="G32" s="19" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A33" s="18">
+        <f>macozonas!A58</f>
+        <v>57</v>
+      </c>
+      <c r="B33" s="19" t="str">
+        <f>_xlfn.CONCAT(macozonas!D58," - ",macozonas!E58)</f>
+        <v>Envigado - Z. Centro</v>
+      </c>
+      <c r="C33" s="19" t="s">
+        <v>186</v>
+      </c>
+      <c r="G33" s="19" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A34" s="18">
+        <f>macozonas!A44</f>
+        <v>43</v>
+      </c>
+      <c r="B34" s="19" t="str">
+        <f>_xlfn.CONCAT(macozonas!D44," - ",macozonas!E44)</f>
+        <v>Girardota - Rural</v>
+      </c>
+      <c r="C34" s="19" t="s">
+        <v>187</v>
+      </c>
+      <c r="G34" s="19" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A35" s="18">
+        <f>macozonas!A28</f>
+        <v>27</v>
+      </c>
+      <c r="B35" s="19" t="str">
+        <f>_xlfn.CONCAT(macozonas!D28," - ",macozonas!E28)</f>
+        <v>Girardota - Urbana</v>
+      </c>
+      <c r="C35" s="19" t="s">
+        <v>173</v>
+      </c>
+      <c r="G35" s="19" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A36" s="18">
+        <f>macozonas!A3</f>
+        <v>2</v>
+      </c>
+      <c r="B36" s="19" t="str">
+        <f>_xlfn.CONCAT(macozonas!D3," - ",macozonas!E3)</f>
+        <v>Itagüí - Calatrava</v>
+      </c>
+      <c r="C36" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="G36" s="19" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A37" s="18">
+        <f>macozonas!A2</f>
+        <v>1</v>
+      </c>
+      <c r="B37" s="19" t="str">
+        <f>_xlfn.CONCAT(macozonas!D2," - ",macozonas!E2)</f>
+        <v>Itagüí - El Rosario</v>
+      </c>
+      <c r="C37" s="19" t="s">
+        <v>216</v>
+      </c>
+      <c r="G37" s="19" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A38" s="18">
+        <f>macozonas!A50</f>
+        <v>49</v>
+      </c>
+      <c r="B38" s="19" t="str">
+        <f>_xlfn.CONCAT(macozonas!D50," - ",macozonas!E50)</f>
+        <v>Itagüí - Rural</v>
+      </c>
+      <c r="C38" s="19" t="s">
+        <v>218</v>
+      </c>
+      <c r="G38" s="19" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A39" s="18">
+        <f>macozonas!A5</f>
+        <v>4</v>
+      </c>
+      <c r="B39" s="19" t="str">
+        <f>_xlfn.CONCAT(macozonas!D5," - ",macozonas!E5)</f>
+        <v>Itagüí - San Francisco</v>
+      </c>
+      <c r="C39" s="19" t="s">
+        <v>188</v>
+      </c>
+      <c r="G39" s="19" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A40" s="18">
+        <f>macozonas!A8</f>
+        <v>7</v>
+      </c>
+      <c r="B40" s="19" t="str">
+        <f>_xlfn.CONCAT(macozonas!D8," - ",macozonas!E8)</f>
+        <v>Itagüí - San Pio</v>
+      </c>
+      <c r="C40" s="19" t="s">
+        <v>184</v>
+      </c>
+      <c r="G40" s="19" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A41" s="18">
+        <f>macozonas!A4</f>
+        <v>3</v>
+      </c>
+      <c r="B41" s="19" t="str">
+        <f>_xlfn.CONCAT(macozonas!D4," - ",macozonas!E4)</f>
+        <v>Itagüí - Santa Maria</v>
+      </c>
+      <c r="C41" s="19" t="s">
+        <v>189</v>
+      </c>
+      <c r="G41" s="19" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A42" s="18">
+        <f>macozonas!A24</f>
+        <v>23</v>
+      </c>
+      <c r="B42" s="19" t="str">
+        <f>_xlfn.CONCAT(macozonas!D24," - ",macozonas!E24)</f>
+        <v>Itagüí - Z. Centro</v>
+      </c>
+      <c r="C42" s="19" t="s">
+        <v>165</v>
+      </c>
+      <c r="G42" s="19" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A43" s="18">
+        <f>macozonas!A51</f>
+        <v>50</v>
+      </c>
+      <c r="B43" s="19" t="str">
+        <f>_xlfn.CONCAT(macozonas!D51," - ",macozonas!E51)</f>
+        <v>La Estrella - Rural</v>
+      </c>
+      <c r="C43" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="G43" s="19" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A44" s="18">
+        <f>macozonas!A26</f>
+        <v>25</v>
+      </c>
+      <c r="B44" s="19" t="str">
+        <f>_xlfn.CONCAT(macozonas!D26," - ",macozonas!E26)</f>
+        <v>La Estrella - Urbana</v>
+      </c>
+      <c r="C44" s="19" t="s">
+        <v>181</v>
+      </c>
+      <c r="G44" s="19" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A45" s="18">
+        <f>macozonas!A18</f>
+        <v>17</v>
+      </c>
+      <c r="B45" s="19" t="str">
+        <f>_xlfn.CONCAT(macozonas!D18," - ",macozonas!E18)</f>
+        <v>Medellín - Aranjuez</v>
+      </c>
+      <c r="C45" s="19" t="s">
+        <v>191</v>
+      </c>
+      <c r="G45" s="19" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A46" s="18">
+        <f>macozonas!A17</f>
+        <v>16</v>
+      </c>
+      <c r="B46" s="19" t="str">
+        <f>_xlfn.CONCAT(macozonas!D17," - ",macozonas!E17)</f>
+        <v>Medellín - Belén</v>
+      </c>
+      <c r="C46" s="19" t="s">
+        <v>210</v>
+      </c>
+      <c r="G46" s="19" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A47" s="18">
+        <f>macozonas!A16</f>
+        <v>15</v>
+      </c>
+      <c r="B47" s="19" t="str">
+        <f>_xlfn.CONCAT(macozonas!D16," - ",macozonas!E16)</f>
+        <v>Medellín - Buenos Aires</v>
+      </c>
+      <c r="C47" s="19" t="s">
+        <v>213</v>
+      </c>
+      <c r="G47" s="19" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A48" s="18">
+        <f>macozonas!A31</f>
+        <v>30</v>
+      </c>
+      <c r="B48" s="19" t="str">
+        <f>_xlfn.CONCAT(macozonas!D31," - ",macozonas!E31)</f>
+        <v>Medellín - Castilla</v>
+      </c>
+      <c r="C48" s="19" t="s">
+        <v>221</v>
+      </c>
+      <c r="G48" s="19" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A49" s="18">
+        <f>macozonas!A47</f>
+        <v>46</v>
+      </c>
+      <c r="B49" s="19" t="str">
+        <f>_xlfn.CONCAT(macozonas!D47," - ",macozonas!E47)</f>
+        <v>Medellín - Corregimiento Altavista</v>
+      </c>
+      <c r="C49" s="19" t="s">
+        <v>220</v>
+      </c>
+      <c r="G49" s="19" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A50" s="18">
+        <f>macozonas!A49</f>
+        <v>48</v>
+      </c>
+      <c r="B50" s="19" t="str">
+        <f>_xlfn.CONCAT(macozonas!D49," - ",macozonas!E49)</f>
+        <v>Medellín - Corregimiento San Antonio</v>
+      </c>
+      <c r="C50" s="19" t="s">
+        <v>222</v>
+      </c>
+      <c r="G50" s="19" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A51" s="18">
+        <f>macozonas!A46</f>
+        <v>45</v>
+      </c>
+      <c r="B51" s="19" t="str">
+        <f>_xlfn.CONCAT(macozonas!D46," - ",macozonas!E46)</f>
+        <v>Medellín - Corregimiento San Cristóbal</v>
+      </c>
+      <c r="C51" s="19" t="s">
+        <v>228</v>
+      </c>
+      <c r="G51" s="19" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A52" s="18">
+        <f>macozonas!A45</f>
+        <v>44</v>
+      </c>
+      <c r="B52" s="19" t="str">
+        <f>_xlfn.CONCAT(macozonas!D45," - ",macozonas!E45)</f>
+        <v>Medellín - Corregimiento San Sebastián</v>
+      </c>
+      <c r="C52" s="19" t="s">
+        <v>219</v>
+      </c>
+      <c r="G52" s="19" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A53" s="18">
+        <f>macozonas!A48</f>
+        <v>47</v>
+      </c>
+      <c r="B53" s="19" t="str">
+        <f>_xlfn.CONCAT(macozonas!D48," - ",macozonas!E48)</f>
+        <v>Medellín - Corregimiento Santa Elena</v>
+      </c>
+      <c r="C53" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="G53" s="19" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A54" s="18">
+        <f>macozonas!A33</f>
+        <v>32</v>
+      </c>
+      <c r="B54" s="19" t="str">
+        <f>_xlfn.CONCAT(macozonas!D33," - ",macozonas!E33)</f>
+        <v>Medellín - Doce de Octubre</v>
+      </c>
+      <c r="C54" s="19" t="s">
+        <v>212</v>
+      </c>
+      <c r="G54" s="19" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A55" s="18">
+        <f>macozonas!A13</f>
+        <v>12</v>
+      </c>
+      <c r="B55" s="19" t="str">
+        <f>_xlfn.CONCAT(macozonas!D13," - ",macozonas!E13)</f>
+        <v>Medellín - El Poblado</v>
+      </c>
+      <c r="C55" s="19" t="s">
+        <v>168</v>
+      </c>
+      <c r="G55" s="19" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A56" s="18">
+        <f>macozonas!A15</f>
+        <v>14</v>
+      </c>
+      <c r="B56" s="19" t="str">
+        <f>_xlfn.CONCAT(macozonas!D15," - ",macozonas!E15)</f>
+        <v>Medellín - Guayabal</v>
+      </c>
+      <c r="C56" s="19" t="s">
+        <v>224</v>
+      </c>
+      <c r="G56" s="19" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A57" s="18">
+        <f>macozonas!A19</f>
+        <v>18</v>
+      </c>
+      <c r="B57" s="19" t="str">
+        <f>_xlfn.CONCAT(macozonas!D19," - ",macozonas!E19)</f>
+        <v>Medellín - La América</v>
+      </c>
+      <c r="C57" s="19" t="s">
+        <v>192</v>
+      </c>
+      <c r="G57" s="19" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A58" s="18">
+        <f>macozonas!A20</f>
+        <v>19</v>
+      </c>
+      <c r="B58" s="19" t="str">
+        <f>_xlfn.CONCAT(macozonas!D20," - ",macozonas!E20)</f>
+        <v>Medellín - La Candelaria</v>
+      </c>
+      <c r="C58" s="19" t="s">
+        <v>171</v>
+      </c>
+      <c r="G58" s="19" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A59" s="18">
+        <f>macozonas!A22</f>
+        <v>21</v>
+      </c>
+      <c r="B59" s="19" t="str">
+        <f>_xlfn.CONCAT(macozonas!D22," - ",macozonas!E22)</f>
+        <v>Medellín - Laureles-Estadio</v>
+      </c>
+      <c r="C59" s="19" t="s">
+        <v>223</v>
+      </c>
+      <c r="G59" s="19" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A60" s="18">
+        <f>macozonas!A14</f>
+        <v>13</v>
+      </c>
+      <c r="B60" s="19" t="str">
+        <f>_xlfn.CONCAT(macozonas!D14," - ",macozonas!E14)</f>
+        <v>Medellín - Manrique</v>
+      </c>
+      <c r="C60" s="19" t="s">
+        <v>229</v>
+      </c>
+      <c r="G60" s="19" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A61" s="18">
+        <f>macozonas!A32</f>
+        <v>31</v>
+      </c>
+      <c r="B61" s="19" t="str">
+        <f>_xlfn.CONCAT(macozonas!D32," - ",macozonas!E32)</f>
+        <v>Medellín - Popular</v>
+      </c>
+      <c r="C61" s="19" t="s">
+        <v>217</v>
+      </c>
+      <c r="G61" s="19" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A62" s="18">
+        <f>macozonas!A12</f>
+        <v>11</v>
+      </c>
+      <c r="B62" s="19" t="str">
+        <f>_xlfn.CONCAT(macozonas!D12," - ",macozonas!E12)</f>
+        <v>Medellín - Robledo</v>
+      </c>
+      <c r="C62" s="19" t="s">
+        <v>227</v>
+      </c>
+      <c r="G62" s="19" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A63" s="18">
+        <f>macozonas!A23</f>
+        <v>22</v>
+      </c>
+      <c r="B63" s="19" t="str">
+        <f>_xlfn.CONCAT(macozonas!D23," - ",macozonas!E23)</f>
+        <v>Medellín - San Javier</v>
+      </c>
+      <c r="C63" s="19" t="s">
+        <v>225</v>
+      </c>
+      <c r="G63" s="19" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A64" s="18">
+        <f>macozonas!A34</f>
+        <v>33</v>
+      </c>
+      <c r="B64" s="19" t="str">
+        <f>_xlfn.CONCAT(macozonas!D34," - ",macozonas!E34)</f>
+        <v>Medellín - Santa Cruz</v>
+      </c>
+      <c r="C64" s="19" t="s">
+        <v>226</v>
+      </c>
+      <c r="G64" s="19" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A65" s="18">
+        <f>macozonas!A21</f>
+        <v>20</v>
+      </c>
+      <c r="B65" s="19" t="str">
+        <f>_xlfn.CONCAT(macozonas!D21," - ",macozonas!E21)</f>
+        <v>Medellín - Villa Hermosa</v>
+      </c>
+      <c r="C65" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="D65" t="s">
+        <v>232</v>
+      </c>
+      <c r="G65" s="19" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A66" s="18">
+        <f>macozonas!A66</f>
+        <v>65</v>
+      </c>
+      <c r="B66" s="19" t="str">
+        <f>_xlfn.CONCAT(macozonas!D66," - ",macozonas!E66)</f>
+        <v>Sabaneta - Rural</v>
+      </c>
+      <c r="C66" s="19" t="s">
+        <v>230</v>
+      </c>
+      <c r="D66" t="s">
+        <v>232</v>
+      </c>
+      <c r="G66" s="19" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A67" s="18">
+        <f>macozonas!A65</f>
+        <v>64</v>
+      </c>
+      <c r="B67" s="19" t="str">
+        <f>_xlfn.CONCAT(macozonas!D65," - ",macozonas!E65)</f>
+        <v>Sabaneta - Urbana</v>
+      </c>
+      <c r="C67" s="19" t="s">
+        <v>231</v>
+      </c>
+      <c r="D67" s="21"/>
+      <c r="G67" s="19" t="s">
+        <v>231</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:C1" xr:uid="{443896CA-5C07-4245-B3AF-BB7D297B88CA}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C67">
+      <sortCondition ref="B1"/>
+    </sortState>
+  </autoFilter>
+  <conditionalFormatting sqref="B2:B67">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>COUNTIF($C$2:$C$67, B2) &gt; 0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -8847,7 +9627,7 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="22" t="s">
         <v>95</v>
       </c>
       <c r="B2" s="13">
@@ -8861,7 +9641,7 @@
       </c>
     </row>
     <row r="3" spans="1:4" ht="24" x14ac:dyDescent="0.3">
-      <c r="A3" s="16"/>
+      <c r="A3" s="23"/>
       <c r="B3" s="13">
         <v>801</v>
       </c>
@@ -8873,7 +9653,7 @@
       </c>
     </row>
     <row r="4" spans="1:4" ht="24" x14ac:dyDescent="0.3">
-      <c r="A4" s="16"/>
+      <c r="A4" s="23"/>
       <c r="B4" s="13">
         <v>802</v>
       </c>
@@ -8885,7 +9665,7 @@
       </c>
     </row>
     <row r="5" spans="1:4" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A5" s="16"/>
+      <c r="A5" s="23"/>
       <c r="B5" s="13">
         <v>803</v>
       </c>
@@ -8897,7 +9677,7 @@
       </c>
     </row>
     <row r="6" spans="1:4" ht="24" x14ac:dyDescent="0.3">
-      <c r="A6" s="16"/>
+      <c r="A6" s="23"/>
       <c r="B6" s="13">
         <v>804</v>
       </c>
@@ -8909,7 +9689,7 @@
       </c>
     </row>
     <row r="7" spans="1:4" ht="35.4" x14ac:dyDescent="0.3">
-      <c r="A7" s="16"/>
+      <c r="A7" s="23"/>
       <c r="B7" s="13">
         <v>805</v>
       </c>
@@ -8921,7 +9701,7 @@
       </c>
     </row>
     <row r="8" spans="1:4" ht="35.4" x14ac:dyDescent="0.3">
-      <c r="A8" s="16"/>
+      <c r="A8" s="23"/>
       <c r="B8" s="13">
         <v>806</v>
       </c>
@@ -8933,7 +9713,7 @@
       </c>
     </row>
     <row r="9" spans="1:4" ht="35.4" x14ac:dyDescent="0.3">
-      <c r="A9" s="17"/>
+      <c r="A9" s="24"/>
       <c r="B9" s="13">
         <v>807</v>
       </c>
@@ -8945,7 +9725,7 @@
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="15" t="s">
+      <c r="A10" s="22" t="s">
         <v>112</v>
       </c>
       <c r="B10" s="13">
@@ -8959,7 +9739,7 @@
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="16"/>
+      <c r="A11" s="23"/>
       <c r="B11" s="13">
         <v>809</v>
       </c>
@@ -8971,7 +9751,7 @@
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="16"/>
+      <c r="A12" s="23"/>
       <c r="B12" s="13">
         <v>810</v>
       </c>
@@ -8983,7 +9763,7 @@
       </c>
     </row>
     <row r="13" spans="1:4" ht="24" x14ac:dyDescent="0.3">
-      <c r="A13" s="16"/>
+      <c r="A13" s="23"/>
       <c r="B13" s="13">
         <v>811</v>
       </c>
@@ -8995,7 +9775,7 @@
       </c>
     </row>
     <row r="14" spans="1:4" ht="35.4" x14ac:dyDescent="0.3">
-      <c r="A14" s="17"/>
+      <c r="A14" s="24"/>
       <c r="B14" s="13">
         <v>812</v>
       </c>
